--- a/docs/freigabe-katalog/versand-2026-10-25-neue-eintraege/recht/Betriebsklar-Freigabe-Katalog-Rechtsanwalt-neue-Eintraege.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-neue-eintraege/recht/Betriebsklar-Freigabe-Katalog-Rechtsanwalt-neue-Eintraege.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Einträge" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="So geht's" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prüfvermerk" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einträge'!$A$1:$Q$2</definedName>
@@ -711,96 +710,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Nach der Rücksendung tragen wir je freigegebenem Eintrag Ihren Namen und das Datum ein; der Hinweis „fachlich noch nicht geprüft“ entfällt dann für diesen Eintrag.</t>
+          <t>Nach Ihrer Bestätigung zeigt die App bei jedem freigegebenen Eintrag einen Prüfvermerk mit Ihrer Rolle (z. B. „von einem Rechtsanwalt“), nie mit Ihrem Namen, und nur für die geprüfte Version; der Hinweis „fachlich noch nicht geprüft“ entfällt dann für diesen Eintrag.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Bitte am Ende das Blatt „Prüfvermerk“ ausfüllen und unterschreiben (Scan genügt).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Prüfvermerk</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Ich habe den Eintrag im Blatt „Einträge“ in der dort genannten Version fachlich geprüft, einschließlich Erklärung und Zuständiger Stelle. Mit „freigegeben“ markierte Einträge sind in allen Spalten zutreffend; für „ändern“ gelten meine Anmerkungen.</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Stand der Prüfung (Datum):</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Name, Funktion:</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Rechtsanwalt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Ort, Datum, Unterschrift:</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Darf Betriebsklar in der App bei den freigegebenen Einträgen angeben „fachlich geprüft von &lt;Name&gt;, &lt;Funktion&gt; (Stand &lt;Datum&gt;)“?</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>ja / nein / anderer Wortlaut:</t>
+          <t>Bitte bestätigen Sie Ihr Ergebnis per E-Mail – eine Unterschrift ist nicht nötig: Nennen Sie in Ihrer Antwort die freigegebenen Einträge mit Version (z. B. „personal.kuenstlersozialabgabe v1 freigegeben“) und schicken Sie diese Datei mit der ausgefüllten Spalte „Entscheidung“ mit.</t>
         </is>
       </c>
     </row>
